--- a/examples/extensions/thai_bim/examples/stair-L-BBS.xlsx
+++ b/examples/extensions/thai_bim/examples/stair-L-BBS.xlsx
@@ -228,7 +228,7 @@
       </c>
       <c r="N2" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">bd5e3d25943044e2</t>
+          <t xml:space="preserve">dbda8e2c16fd44c0</t>
         </is>
       </c>
       <c r="O2" s="0" t="inlineStr">
@@ -334,7 +334,7 @@
       </c>
       <c r="N3" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">bd5e3d25943044e2</t>
+          <t xml:space="preserve">dbda8e2c16fd44c0</t>
         </is>
       </c>
       <c r="O3" s="0" t="inlineStr">
@@ -440,7 +440,7 @@
       </c>
       <c r="N4" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">bd5e3d25943044e2</t>
+          <t xml:space="preserve">dbda8e2c16fd44c0</t>
         </is>
       </c>
       <c r="O4" s="0" t="inlineStr">
@@ -546,7 +546,7 @@
       </c>
       <c r="N5" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">bd5e3d25943044e2</t>
+          <t xml:space="preserve">dbda8e2c16fd44c0</t>
         </is>
       </c>
       <c r="O5" s="0" t="inlineStr">
@@ -652,7 +652,7 @@
       </c>
       <c r="N6" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">bd5e3d25943044e2</t>
+          <t xml:space="preserve">dbda8e2c16fd44c0</t>
         </is>
       </c>
       <c r="O6" s="0" t="inlineStr">
@@ -758,7 +758,7 @@
       </c>
       <c r="N7" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">bd5e3d25943044e2</t>
+          <t xml:space="preserve">dbda8e2c16fd44c0</t>
         </is>
       </c>
       <c r="O7" s="0" t="inlineStr">
@@ -864,7 +864,7 @@
       </c>
       <c r="N8" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">bd5e3d25943044e2</t>
+          <t xml:space="preserve">dbda8e2c16fd44c0</t>
         </is>
       </c>
       <c r="O8" s="0" t="inlineStr">
@@ -970,7 +970,7 @@
       </c>
       <c r="N9" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">bd5e3d25943044e2</t>
+          <t xml:space="preserve">dbda8e2c16fd44c0</t>
         </is>
       </c>
       <c r="O9" s="0" t="inlineStr">
@@ -1076,7 +1076,7 @@
       </c>
       <c r="N10" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">bd5e3d25943044e2</t>
+          <t xml:space="preserve">dbda8e2c16fd44c0</t>
         </is>
       </c>
       <c r="O10" s="0" t="inlineStr">
@@ -1182,7 +1182,7 @@
       </c>
       <c r="N11" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">bd5e3d25943044e2</t>
+          <t xml:space="preserve">dbda8e2c16fd44c0</t>
         </is>
       </c>
       <c r="O11" s="0" t="inlineStr">
@@ -1328,12 +1328,12 @@
     <row r="2">
       <c r="A2" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">3402a664e6204f57</t>
+          <t xml:space="preserve">a1f701f232d94f9e</t>
         </is>
       </c>
       <c r="B2" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">bd5e3d25943044e2</t>
+          <t xml:space="preserve">dbda8e2c16fd44c0</t>
         </is>
       </c>
       <c r="C2" s="0" t="inlineStr">
@@ -1401,12 +1401,12 @@
     <row r="3">
       <c r="A3" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">6ce6c69b48fe4bec</t>
+          <t xml:space="preserve">5df2c5da5983455c</t>
         </is>
       </c>
       <c r="B3" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">bd5e3d25943044e2</t>
+          <t xml:space="preserve">dbda8e2c16fd44c0</t>
         </is>
       </c>
       <c r="C3" s="0" t="inlineStr">
@@ -1474,12 +1474,12 @@
     <row r="4">
       <c r="A4" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">ef4231f472f744a0</t>
+          <t xml:space="preserve">0cd3acc053a841f7</t>
         </is>
       </c>
       <c r="B4" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">bd5e3d25943044e2</t>
+          <t xml:space="preserve">dbda8e2c16fd44c0</t>
         </is>
       </c>
       <c r="C4" s="0" t="inlineStr">
@@ -1547,12 +1547,12 @@
     <row r="5">
       <c r="A5" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">8bc08cbaa3264bc7</t>
+          <t xml:space="preserve">89d134f537b34fc7</t>
         </is>
       </c>
       <c r="B5" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">bd5e3d25943044e2</t>
+          <t xml:space="preserve">dbda8e2c16fd44c0</t>
         </is>
       </c>
       <c r="C5" s="0" t="inlineStr">
@@ -1620,12 +1620,12 @@
     <row r="6">
       <c r="A6" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">b6c69f6bc3fd410a</t>
+          <t xml:space="preserve">4d7a2efdbe984536</t>
         </is>
       </c>
       <c r="B6" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">bd5e3d25943044e2</t>
+          <t xml:space="preserve">dbda8e2c16fd44c0</t>
         </is>
       </c>
       <c r="C6" s="0" t="inlineStr">
@@ -1693,12 +1693,12 @@
     <row r="7">
       <c r="A7" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">003730b719c44403</t>
+          <t xml:space="preserve">298f73c451044f87</t>
         </is>
       </c>
       <c r="B7" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">bd5e3d25943044e2</t>
+          <t xml:space="preserve">dbda8e2c16fd44c0</t>
         </is>
       </c>
       <c r="C7" s="0" t="inlineStr">
@@ -1766,12 +1766,12 @@
     <row r="8">
       <c r="A8" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">9a54c82c9a4541fc</t>
+          <t xml:space="preserve">1dd37b6956cc4f7c</t>
         </is>
       </c>
       <c r="B8" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">bd5e3d25943044e2</t>
+          <t xml:space="preserve">dbda8e2c16fd44c0</t>
         </is>
       </c>
       <c r="C8" s="0" t="inlineStr">
@@ -1839,12 +1839,12 @@
     <row r="9">
       <c r="A9" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">044653f36e1d4653</t>
+          <t xml:space="preserve">ea558abf782f41c1</t>
         </is>
       </c>
       <c r="B9" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">bd5e3d25943044e2</t>
+          <t xml:space="preserve">dbda8e2c16fd44c0</t>
         </is>
       </c>
       <c r="C9" s="0" t="inlineStr">
@@ -1912,12 +1912,12 @@
     <row r="10">
       <c r="A10" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">a2119e9396694f79</t>
+          <t xml:space="preserve">76fd453154674faa</t>
         </is>
       </c>
       <c r="B10" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">bd5e3d25943044e2</t>
+          <t xml:space="preserve">dbda8e2c16fd44c0</t>
         </is>
       </c>
       <c r="C10" s="0" t="inlineStr">
@@ -1985,12 +1985,12 @@
     <row r="11">
       <c r="A11" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">edf72fa58bf14bd1</t>
+          <t xml:space="preserve">51d83a62615043d5</t>
         </is>
       </c>
       <c r="B11" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">bd5e3d25943044e2</t>
+          <t xml:space="preserve">dbda8e2c16fd44c0</t>
         </is>
       </c>
       <c r="C11" s="0" t="inlineStr">
@@ -2058,12 +2058,12 @@
     <row r="12">
       <c r="A12" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">716cad37ba134e01</t>
+          <t xml:space="preserve">52f6503048964ad9</t>
         </is>
       </c>
       <c r="B12" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">bd5e3d25943044e2</t>
+          <t xml:space="preserve">dbda8e2c16fd44c0</t>
         </is>
       </c>
       <c r="C12" s="0" t="inlineStr">
@@ -2131,12 +2131,12 @@
     <row r="13">
       <c r="A13" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">4c361bed5d1d4e08</t>
+          <t xml:space="preserve">57cf659cc9114000</t>
         </is>
       </c>
       <c r="B13" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">bd5e3d25943044e2</t>
+          <t xml:space="preserve">dbda8e2c16fd44c0</t>
         </is>
       </c>
       <c r="C13" s="0" t="inlineStr">
@@ -2204,12 +2204,12 @@
     <row r="14">
       <c r="A14" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">84760e3d218f4270</t>
+          <t xml:space="preserve">6707c176ee6f4cb0</t>
         </is>
       </c>
       <c r="B14" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">bd5e3d25943044e2</t>
+          <t xml:space="preserve">dbda8e2c16fd44c0</t>
         </is>
       </c>
       <c r="C14" s="0" t="inlineStr">
@@ -2277,12 +2277,12 @@
     <row r="15">
       <c r="A15" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">79c408a88a0a4d90</t>
+          <t xml:space="preserve">f06f612e604646fe</t>
         </is>
       </c>
       <c r="B15" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">bd5e3d25943044e2</t>
+          <t xml:space="preserve">dbda8e2c16fd44c0</t>
         </is>
       </c>
       <c r="C15" s="0" t="inlineStr">
@@ -2350,12 +2350,12 @@
     <row r="16">
       <c r="A16" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">8b37aa99e0d24728</t>
+          <t xml:space="preserve">a2d580602af6428b</t>
         </is>
       </c>
       <c r="B16" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">bd5e3d25943044e2</t>
+          <t xml:space="preserve">dbda8e2c16fd44c0</t>
         </is>
       </c>
       <c r="C16" s="0" t="inlineStr">
@@ -2423,12 +2423,12 @@
     <row r="17">
       <c r="A17" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">a9047fafb6964eef</t>
+          <t xml:space="preserve">7ae16617b5f646c2</t>
         </is>
       </c>
       <c r="B17" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">bd5e3d25943044e2</t>
+          <t xml:space="preserve">dbda8e2c16fd44c0</t>
         </is>
       </c>
       <c r="C17" s="0" t="inlineStr">
@@ -2496,12 +2496,12 @@
     <row r="18">
       <c r="A18" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">2b1298a66067455c</t>
+          <t xml:space="preserve">754386c39c934923</t>
         </is>
       </c>
       <c r="B18" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">bd5e3d25943044e2</t>
+          <t xml:space="preserve">dbda8e2c16fd44c0</t>
         </is>
       </c>
       <c r="C18" s="0" t="inlineStr">
@@ -2569,12 +2569,12 @@
     <row r="19">
       <c r="A19" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">d790cd345fa54270</t>
+          <t xml:space="preserve">8165314304c248b4</t>
         </is>
       </c>
       <c r="B19" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">bd5e3d25943044e2</t>
+          <t xml:space="preserve">dbda8e2c16fd44c0</t>
         </is>
       </c>
       <c r="C19" s="0" t="inlineStr">
@@ -2642,12 +2642,12 @@
     <row r="20">
       <c r="A20" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">3ddea4eaaba8467b</t>
+          <t xml:space="preserve">d11aee1ea9e4445f</t>
         </is>
       </c>
       <c r="B20" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">bd5e3d25943044e2</t>
+          <t xml:space="preserve">dbda8e2c16fd44c0</t>
         </is>
       </c>
       <c r="C20" s="0" t="inlineStr">
@@ -2715,12 +2715,12 @@
     <row r="21">
       <c r="A21" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">69e1e90b30e2488b</t>
+          <t xml:space="preserve">f2568ef980d847ff</t>
         </is>
       </c>
       <c r="B21" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">bd5e3d25943044e2</t>
+          <t xml:space="preserve">dbda8e2c16fd44c0</t>
         </is>
       </c>
       <c r="C21" s="0" t="inlineStr">
@@ -2788,12 +2788,12 @@
     <row r="22">
       <c r="A22" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">c58d9658651449b1</t>
+          <t xml:space="preserve">2ff46376c8ff45cf</t>
         </is>
       </c>
       <c r="B22" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">bd5e3d25943044e2</t>
+          <t xml:space="preserve">dbda8e2c16fd44c0</t>
         </is>
       </c>
       <c r="C22" s="0" t="inlineStr">
@@ -2861,12 +2861,12 @@
     <row r="23">
       <c r="A23" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">80c6354f089542ad</t>
+          <t xml:space="preserve">fc8e16ca37fc4393</t>
         </is>
       </c>
       <c r="B23" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">bd5e3d25943044e2</t>
+          <t xml:space="preserve">dbda8e2c16fd44c0</t>
         </is>
       </c>
       <c r="C23" s="0" t="inlineStr">
@@ -2934,12 +2934,12 @@
     <row r="24">
       <c r="A24" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">997e267c0607472e</t>
+          <t xml:space="preserve">7ae4e8583c6f49b8</t>
         </is>
       </c>
       <c r="B24" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">bd5e3d25943044e2</t>
+          <t xml:space="preserve">dbda8e2c16fd44c0</t>
         </is>
       </c>
       <c r="C24" s="0" t="inlineStr">
@@ -3007,12 +3007,12 @@
     <row r="25">
       <c r="A25" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">577f5bf3e0cf4c16</t>
+          <t xml:space="preserve">9622e0c2627b4031</t>
         </is>
       </c>
       <c r="B25" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">bd5e3d25943044e2</t>
+          <t xml:space="preserve">dbda8e2c16fd44c0</t>
         </is>
       </c>
       <c r="C25" s="0" t="inlineStr">
@@ -3080,12 +3080,12 @@
     <row r="26">
       <c r="A26" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">05fc4050c32b49fa</t>
+          <t xml:space="preserve">68b83e5f90234860</t>
         </is>
       </c>
       <c r="B26" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">bd5e3d25943044e2</t>
+          <t xml:space="preserve">dbda8e2c16fd44c0</t>
         </is>
       </c>
       <c r="C26" s="0" t="inlineStr">
@@ -3153,12 +3153,12 @@
     <row r="27">
       <c r="A27" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">5538b2ea25914ad8</t>
+          <t xml:space="preserve">0d14260c296d48f9</t>
         </is>
       </c>
       <c r="B27" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">bd5e3d25943044e2</t>
+          <t xml:space="preserve">dbda8e2c16fd44c0</t>
         </is>
       </c>
       <c r="C27" s="0" t="inlineStr">
@@ -3226,12 +3226,12 @@
     <row r="28">
       <c r="A28" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">6fce31d60aa14a6a</t>
+          <t xml:space="preserve">fb4d29a707a347ec</t>
         </is>
       </c>
       <c r="B28" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">bd5e3d25943044e2</t>
+          <t xml:space="preserve">dbda8e2c16fd44c0</t>
         </is>
       </c>
       <c r="C28" s="0" t="inlineStr">
@@ -3299,12 +3299,12 @@
     <row r="29">
       <c r="A29" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">9deb87ba83df41c5</t>
+          <t xml:space="preserve">024d777234614fed</t>
         </is>
       </c>
       <c r="B29" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">bd5e3d25943044e2</t>
+          <t xml:space="preserve">dbda8e2c16fd44c0</t>
         </is>
       </c>
       <c r="C29" s="0" t="inlineStr">
@@ -3372,12 +3372,12 @@
     <row r="30">
       <c r="A30" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">2ee43ae12e194af1</t>
+          <t xml:space="preserve">3ac3c6e29e4f45a0</t>
         </is>
       </c>
       <c r="B30" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">bd5e3d25943044e2</t>
+          <t xml:space="preserve">dbda8e2c16fd44c0</t>
         </is>
       </c>
       <c r="C30" s="0" t="inlineStr">
@@ -3445,12 +3445,12 @@
     <row r="31">
       <c r="A31" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">ed10486d463d4ee5</t>
+          <t xml:space="preserve">92207e9df1944ebf</t>
         </is>
       </c>
       <c r="B31" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">bd5e3d25943044e2</t>
+          <t xml:space="preserve">dbda8e2c16fd44c0</t>
         </is>
       </c>
       <c r="C31" s="0" t="inlineStr">
@@ -3518,12 +3518,12 @@
     <row r="32">
       <c r="A32" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">6eb81baa82684c94</t>
+          <t xml:space="preserve">be3a03e45f1045e5</t>
         </is>
       </c>
       <c r="B32" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">bd5e3d25943044e2</t>
+          <t xml:space="preserve">dbda8e2c16fd44c0</t>
         </is>
       </c>
       <c r="C32" s="0" t="inlineStr">
@@ -3591,12 +3591,12 @@
     <row r="33">
       <c r="A33" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">186b3d472e104357</t>
+          <t xml:space="preserve">e6107fdfe2ed4a9f</t>
         </is>
       </c>
       <c r="B33" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">bd5e3d25943044e2</t>
+          <t xml:space="preserve">dbda8e2c16fd44c0</t>
         </is>
       </c>
       <c r="C33" s="0" t="inlineStr">
@@ -3664,12 +3664,12 @@
     <row r="34">
       <c r="A34" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">a7661a87ea694445</t>
+          <t xml:space="preserve">05a17a641d14438e</t>
         </is>
       </c>
       <c r="B34" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">bd5e3d25943044e2</t>
+          <t xml:space="preserve">dbda8e2c16fd44c0</t>
         </is>
       </c>
       <c r="C34" s="0" t="inlineStr">
@@ -3737,12 +3737,12 @@
     <row r="35">
       <c r="A35" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">83ac52f6a46d4e0e</t>
+          <t xml:space="preserve">9ce523bda8de407d</t>
         </is>
       </c>
       <c r="B35" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">bd5e3d25943044e2</t>
+          <t xml:space="preserve">dbda8e2c16fd44c0</t>
         </is>
       </c>
       <c r="C35" s="0" t="inlineStr">
@@ -3810,12 +3810,12 @@
     <row r="36">
       <c r="A36" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">6ea9c397eddd4b7b</t>
+          <t xml:space="preserve">096fdd512afc45b3</t>
         </is>
       </c>
       <c r="B36" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">bd5e3d25943044e2</t>
+          <t xml:space="preserve">dbda8e2c16fd44c0</t>
         </is>
       </c>
       <c r="C36" s="0" t="inlineStr">
@@ -3883,12 +3883,12 @@
     <row r="37">
       <c r="A37" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">a73f125141c3422a</t>
+          <t xml:space="preserve">88a691a6eed04988</t>
         </is>
       </c>
       <c r="B37" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">bd5e3d25943044e2</t>
+          <t xml:space="preserve">dbda8e2c16fd44c0</t>
         </is>
       </c>
       <c r="C37" s="0" t="inlineStr">
@@ -3956,12 +3956,12 @@
     <row r="38">
       <c r="A38" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">8ad91ec302ed41cd</t>
+          <t xml:space="preserve">1f9cf85fd059436e</t>
         </is>
       </c>
       <c r="B38" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">bd5e3d25943044e2</t>
+          <t xml:space="preserve">dbda8e2c16fd44c0</t>
         </is>
       </c>
       <c r="C38" s="0" t="inlineStr">
@@ -4029,12 +4029,12 @@
     <row r="39">
       <c r="A39" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">1cc1436cb804405a</t>
+          <t xml:space="preserve">18ef8282ad684985</t>
         </is>
       </c>
       <c r="B39" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">bd5e3d25943044e2</t>
+          <t xml:space="preserve">dbda8e2c16fd44c0</t>
         </is>
       </c>
       <c r="C39" s="0" t="inlineStr">
@@ -4102,12 +4102,12 @@
     <row r="40">
       <c r="A40" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">f74d9b037ec84a73</t>
+          <t xml:space="preserve">74665cbbd2a44d2e</t>
         </is>
       </c>
       <c r="B40" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">bd5e3d25943044e2</t>
+          <t xml:space="preserve">dbda8e2c16fd44c0</t>
         </is>
       </c>
       <c r="C40" s="0" t="inlineStr">
@@ -4175,12 +4175,12 @@
     <row r="41">
       <c r="A41" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">58ca96702b1e4b8e</t>
+          <t xml:space="preserve">9d4b11850fe14d22</t>
         </is>
       </c>
       <c r="B41" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">bd5e3d25943044e2</t>
+          <t xml:space="preserve">dbda8e2c16fd44c0</t>
         </is>
       </c>
       <c r="C41" s="0" t="inlineStr">
@@ -4248,12 +4248,12 @@
     <row r="42">
       <c r="A42" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">d3ea851c9dc64edc</t>
+          <t xml:space="preserve">224f580cf3514824</t>
         </is>
       </c>
       <c r="B42" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">bd5e3d25943044e2</t>
+          <t xml:space="preserve">dbda8e2c16fd44c0</t>
         </is>
       </c>
       <c r="C42" s="0" t="inlineStr">
@@ -4321,12 +4321,12 @@
     <row r="43">
       <c r="A43" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">e08ab8e0d0124007</t>
+          <t xml:space="preserve">0205651220ed4787</t>
         </is>
       </c>
       <c r="B43" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">bd5e3d25943044e2</t>
+          <t xml:space="preserve">dbda8e2c16fd44c0</t>
         </is>
       </c>
       <c r="C43" s="0" t="inlineStr">
@@ -4394,12 +4394,12 @@
     <row r="44">
       <c r="A44" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">9be1bfb940ea4a78</t>
+          <t xml:space="preserve">205ae43f273f4307</t>
         </is>
       </c>
       <c r="B44" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">bd5e3d25943044e2</t>
+          <t xml:space="preserve">dbda8e2c16fd44c0</t>
         </is>
       </c>
       <c r="C44" s="0" t="inlineStr">
@@ -4467,12 +4467,12 @@
     <row r="45">
       <c r="A45" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">b8d3d366cd1948fc</t>
+          <t xml:space="preserve">fd21ac4343664e88</t>
         </is>
       </c>
       <c r="B45" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">bd5e3d25943044e2</t>
+          <t xml:space="preserve">dbda8e2c16fd44c0</t>
         </is>
       </c>
       <c r="C45" s="0" t="inlineStr">
@@ -4540,12 +4540,12 @@
     <row r="46">
       <c r="A46" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">da6e75fcbd80482f</t>
+          <t xml:space="preserve">3392220fba4141b2</t>
         </is>
       </c>
       <c r="B46" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">bd5e3d25943044e2</t>
+          <t xml:space="preserve">dbda8e2c16fd44c0</t>
         </is>
       </c>
       <c r="C46" s="0" t="inlineStr">
@@ -4613,12 +4613,12 @@
     <row r="47">
       <c r="A47" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">0730c43762444a73</t>
+          <t xml:space="preserve">4b8b62b5273e43ee</t>
         </is>
       </c>
       <c r="B47" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">bd5e3d25943044e2</t>
+          <t xml:space="preserve">dbda8e2c16fd44c0</t>
         </is>
       </c>
       <c r="C47" s="0" t="inlineStr">
@@ -4686,12 +4686,12 @@
     <row r="48">
       <c r="A48" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">feefd144269c4d8a</t>
+          <t xml:space="preserve">cbf2c873feb34d6c</t>
         </is>
       </c>
       <c r="B48" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">bd5e3d25943044e2</t>
+          <t xml:space="preserve">dbda8e2c16fd44c0</t>
         </is>
       </c>
       <c r="C48" s="0" t="inlineStr">
@@ -4759,12 +4759,12 @@
     <row r="49">
       <c r="A49" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">e1a81c843e0c4be7</t>
+          <t xml:space="preserve">fec0aefd64f046b7</t>
         </is>
       </c>
       <c r="B49" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">bd5e3d25943044e2</t>
+          <t xml:space="preserve">dbda8e2c16fd44c0</t>
         </is>
       </c>
       <c r="C49" s="0" t="inlineStr">
@@ -4832,12 +4832,12 @@
     <row r="50">
       <c r="A50" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">c9bc4974d8354bcd</t>
+          <t xml:space="preserve">cc202bdd2b994113</t>
         </is>
       </c>
       <c r="B50" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">bd5e3d25943044e2</t>
+          <t xml:space="preserve">dbda8e2c16fd44c0</t>
         </is>
       </c>
       <c r="C50" s="0" t="inlineStr">
@@ -4905,12 +4905,12 @@
     <row r="51">
       <c r="A51" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">7b2dba70f6224e7d</t>
+          <t xml:space="preserve">b777c744b1364c4f</t>
         </is>
       </c>
       <c r="B51" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">bd5e3d25943044e2</t>
+          <t xml:space="preserve">dbda8e2c16fd44c0</t>
         </is>
       </c>
       <c r="C51" s="0" t="inlineStr">
@@ -4978,12 +4978,12 @@
     <row r="52">
       <c r="A52" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">ed310d58a131435d</t>
+          <t xml:space="preserve">5f3028f1e2f54ddd</t>
         </is>
       </c>
       <c r="B52" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">bd5e3d25943044e2</t>
+          <t xml:space="preserve">dbda8e2c16fd44c0</t>
         </is>
       </c>
       <c r="C52" s="0" t="inlineStr">
@@ -5051,12 +5051,12 @@
     <row r="53">
       <c r="A53" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">866b7739b5694452</t>
+          <t xml:space="preserve">c90fde77b19146cd</t>
         </is>
       </c>
       <c r="B53" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">bd5e3d25943044e2</t>
+          <t xml:space="preserve">dbda8e2c16fd44c0</t>
         </is>
       </c>
       <c r="C53" s="0" t="inlineStr">
@@ -5124,12 +5124,12 @@
     <row r="54">
       <c r="A54" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">c172d42deab9497b</t>
+          <t xml:space="preserve">ee879c75a55f4504</t>
         </is>
       </c>
       <c r="B54" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">bd5e3d25943044e2</t>
+          <t xml:space="preserve">dbda8e2c16fd44c0</t>
         </is>
       </c>
       <c r="C54" s="0" t="inlineStr">
@@ -5197,12 +5197,12 @@
     <row r="55">
       <c r="A55" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">682011d928734352</t>
+          <t xml:space="preserve">50e5cb61fd8d4146</t>
         </is>
       </c>
       <c r="B55" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">bd5e3d25943044e2</t>
+          <t xml:space="preserve">dbda8e2c16fd44c0</t>
         </is>
       </c>
       <c r="C55" s="0" t="inlineStr">
@@ -5270,12 +5270,12 @@
     <row r="56">
       <c r="A56" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">9924e4249927462b</t>
+          <t xml:space="preserve">9204613b44a94663</t>
         </is>
       </c>
       <c r="B56" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">bd5e3d25943044e2</t>
+          <t xml:space="preserve">dbda8e2c16fd44c0</t>
         </is>
       </c>
       <c r="C56" s="0" t="inlineStr">
@@ -5343,12 +5343,12 @@
     <row r="57">
       <c r="A57" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">fa3fe901a67347f3</t>
+          <t xml:space="preserve">644e1097c2104866</t>
         </is>
       </c>
       <c r="B57" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">bd5e3d25943044e2</t>
+          <t xml:space="preserve">dbda8e2c16fd44c0</t>
         </is>
       </c>
       <c r="C57" s="0" t="inlineStr">
@@ -5416,12 +5416,12 @@
     <row r="58">
       <c r="A58" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">0ff85edc09f5461b</t>
+          <t xml:space="preserve">305ae4e0d8df4a3b</t>
         </is>
       </c>
       <c r="B58" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">bd5e3d25943044e2</t>
+          <t xml:space="preserve">dbda8e2c16fd44c0</t>
         </is>
       </c>
       <c r="C58" s="0" t="inlineStr">
@@ -5489,12 +5489,12 @@
     <row r="59">
       <c r="A59" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">d35310bba0b54d4c</t>
+          <t xml:space="preserve">234530a6151343dc</t>
         </is>
       </c>
       <c r="B59" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">bd5e3d25943044e2</t>
+          <t xml:space="preserve">dbda8e2c16fd44c0</t>
         </is>
       </c>
       <c r="C59" s="0" t="inlineStr">
@@ -5562,12 +5562,12 @@
     <row r="60">
       <c r="A60" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">2409649bf1b2466f</t>
+          <t xml:space="preserve">1caa9844ca2c40b9</t>
         </is>
       </c>
       <c r="B60" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">bd5e3d25943044e2</t>
+          <t xml:space="preserve">dbda8e2c16fd44c0</t>
         </is>
       </c>
       <c r="C60" s="0" t="inlineStr">
@@ -5635,12 +5635,12 @@
     <row r="61">
       <c r="A61" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">f6f3eae3611e4744</t>
+          <t xml:space="preserve">6b495d4698ad4e0a</t>
         </is>
       </c>
       <c r="B61" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">bd5e3d25943044e2</t>
+          <t xml:space="preserve">dbda8e2c16fd44c0</t>
         </is>
       </c>
       <c r="C61" s="0" t="inlineStr">
@@ -5708,12 +5708,12 @@
     <row r="62">
       <c r="A62" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">077bbd2c31da4c2f</t>
+          <t xml:space="preserve">3c56d07f993a45bc</t>
         </is>
       </c>
       <c r="B62" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">bd5e3d25943044e2</t>
+          <t xml:space="preserve">dbda8e2c16fd44c0</t>
         </is>
       </c>
       <c r="C62" s="0" t="inlineStr">
@@ -5781,12 +5781,12 @@
     <row r="63">
       <c r="A63" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">0fd8a0fc6af3429b</t>
+          <t xml:space="preserve">6049f36583b548fa</t>
         </is>
       </c>
       <c r="B63" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">bd5e3d25943044e2</t>
+          <t xml:space="preserve">dbda8e2c16fd44c0</t>
         </is>
       </c>
       <c r="C63" s="0" t="inlineStr">
@@ -5854,12 +5854,12 @@
     <row r="64">
       <c r="A64" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">1bbae9d0736c4603</t>
+          <t xml:space="preserve">28718250f5674f58</t>
         </is>
       </c>
       <c r="B64" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">bd5e3d25943044e2</t>
+          <t xml:space="preserve">dbda8e2c16fd44c0</t>
         </is>
       </c>
       <c r="C64" s="0" t="inlineStr">
@@ -5927,12 +5927,12 @@
     <row r="65">
       <c r="A65" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">c11977814ca24257</t>
+          <t xml:space="preserve">193746d19b8f497d</t>
         </is>
       </c>
       <c r="B65" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">bd5e3d25943044e2</t>
+          <t xml:space="preserve">dbda8e2c16fd44c0</t>
         </is>
       </c>
       <c r="C65" s="0" t="inlineStr">
@@ -6000,12 +6000,12 @@
     <row r="66">
       <c r="A66" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">e4a96f9fed704b8a</t>
+          <t xml:space="preserve">79a2695977664f3a</t>
         </is>
       </c>
       <c r="B66" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">bd5e3d25943044e2</t>
+          <t xml:space="preserve">dbda8e2c16fd44c0</t>
         </is>
       </c>
       <c r="C66" s="0" t="inlineStr">
@@ -6073,12 +6073,12 @@
     <row r="67">
       <c r="A67" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">7694e7b41579484a</t>
+          <t xml:space="preserve">1b48a651020c46fa</t>
         </is>
       </c>
       <c r="B67" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">bd5e3d25943044e2</t>
+          <t xml:space="preserve">dbda8e2c16fd44c0</t>
         </is>
       </c>
       <c r="C67" s="0" t="inlineStr">
@@ -6146,12 +6146,12 @@
     <row r="68">
       <c r="A68" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">366a5123f0544f6a</t>
+          <t xml:space="preserve">0a5e3256088f4e4d</t>
         </is>
       </c>
       <c r="B68" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">bd5e3d25943044e2</t>
+          <t xml:space="preserve">dbda8e2c16fd44c0</t>
         </is>
       </c>
       <c r="C68" s="0" t="inlineStr">
@@ -6219,12 +6219,12 @@
     <row r="69">
       <c r="A69" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">b91f0bce45124843</t>
+          <t xml:space="preserve">75a2fe08d0594771</t>
         </is>
       </c>
       <c r="B69" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">bd5e3d25943044e2</t>
+          <t xml:space="preserve">dbda8e2c16fd44c0</t>
         </is>
       </c>
       <c r="C69" s="0" t="inlineStr">
@@ -6292,12 +6292,12 @@
     <row r="70">
       <c r="A70" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">075b460fb79f463f</t>
+          <t xml:space="preserve">74f8ab0ed3774862</t>
         </is>
       </c>
       <c r="B70" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">bd5e3d25943044e2</t>
+          <t xml:space="preserve">dbda8e2c16fd44c0</t>
         </is>
       </c>
       <c r="C70" s="0" t="inlineStr">
@@ -6365,12 +6365,12 @@
     <row r="71">
       <c r="A71" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">9c7d0e8791b04f3e</t>
+          <t xml:space="preserve">97faa008216e4c0a</t>
         </is>
       </c>
       <c r="B71" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">bd5e3d25943044e2</t>
+          <t xml:space="preserve">dbda8e2c16fd44c0</t>
         </is>
       </c>
       <c r="C71" s="0" t="inlineStr">
@@ -6438,12 +6438,12 @@
     <row r="72">
       <c r="A72" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">903ff447ae55453c</t>
+          <t xml:space="preserve">338c64c59cba4c6b</t>
         </is>
       </c>
       <c r="B72" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">bd5e3d25943044e2</t>
+          <t xml:space="preserve">dbda8e2c16fd44c0</t>
         </is>
       </c>
       <c r="C72" s="0" t="inlineStr">
@@ -6511,12 +6511,12 @@
     <row r="73">
       <c r="A73" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">418cd37ae9a543c5</t>
+          <t xml:space="preserve">431b54fabbab4e87</t>
         </is>
       </c>
       <c r="B73" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">bd5e3d25943044e2</t>
+          <t xml:space="preserve">dbda8e2c16fd44c0</t>
         </is>
       </c>
       <c r="C73" s="0" t="inlineStr">
@@ -6584,12 +6584,12 @@
     <row r="74">
       <c r="A74" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">7b28fb3796ae4495</t>
+          <t xml:space="preserve">20490394bcdf442b</t>
         </is>
       </c>
       <c r="B74" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">bd5e3d25943044e2</t>
+          <t xml:space="preserve">dbda8e2c16fd44c0</t>
         </is>
       </c>
       <c r="C74" s="0" t="inlineStr">
@@ -6657,12 +6657,12 @@
     <row r="75">
       <c r="A75" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">f538ef5dd2924229</t>
+          <t xml:space="preserve">7fcad8a894b14892</t>
         </is>
       </c>
       <c r="B75" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">bd5e3d25943044e2</t>
+          <t xml:space="preserve">dbda8e2c16fd44c0</t>
         </is>
       </c>
       <c r="C75" s="0" t="inlineStr">
@@ -6730,12 +6730,12 @@
     <row r="76">
       <c r="A76" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">eedc1d5457e2449c</t>
+          <t xml:space="preserve">d23fddae8da943bb</t>
         </is>
       </c>
       <c r="B76" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">bd5e3d25943044e2</t>
+          <t xml:space="preserve">dbda8e2c16fd44c0</t>
         </is>
       </c>
       <c r="C76" s="0" t="inlineStr">
@@ -6803,12 +6803,12 @@
     <row r="77">
       <c r="A77" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">3d1b56b8978d4a75</t>
+          <t xml:space="preserve">8bf50fd30e0447d3</t>
         </is>
       </c>
       <c r="B77" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">bd5e3d25943044e2</t>
+          <t xml:space="preserve">dbda8e2c16fd44c0</t>
         </is>
       </c>
       <c r="C77" s="0" t="inlineStr">
@@ -6876,12 +6876,12 @@
     <row r="78">
       <c r="A78" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">760a4456fadc4a55</t>
+          <t xml:space="preserve">10e4bc13b85545b6</t>
         </is>
       </c>
       <c r="B78" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">bd5e3d25943044e2</t>
+          <t xml:space="preserve">dbda8e2c16fd44c0</t>
         </is>
       </c>
       <c r="C78" s="0" t="inlineStr">
@@ -6949,12 +6949,12 @@
     <row r="79">
       <c r="A79" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">d1fd093be8f649b0</t>
+          <t xml:space="preserve">a9ee1599378147f7</t>
         </is>
       </c>
       <c r="B79" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">bd5e3d25943044e2</t>
+          <t xml:space="preserve">dbda8e2c16fd44c0</t>
         </is>
       </c>
       <c r="C79" s="0" t="inlineStr">
@@ -7022,12 +7022,12 @@
     <row r="80">
       <c r="A80" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">d4761fd1f2d14fd0</t>
+          <t xml:space="preserve">189dce352cce49ec</t>
         </is>
       </c>
       <c r="B80" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">bd5e3d25943044e2</t>
+          <t xml:space="preserve">dbda8e2c16fd44c0</t>
         </is>
       </c>
       <c r="C80" s="0" t="inlineStr">
@@ -7095,12 +7095,12 @@
     <row r="81">
       <c r="A81" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">a6235a42a5804b47</t>
+          <t xml:space="preserve">30107edfff44479a</t>
         </is>
       </c>
       <c r="B81" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">bd5e3d25943044e2</t>
+          <t xml:space="preserve">dbda8e2c16fd44c0</t>
         </is>
       </c>
       <c r="C81" s="0" t="inlineStr">
@@ -7168,12 +7168,12 @@
     <row r="82">
       <c r="A82" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">e05d71214c224260</t>
+          <t xml:space="preserve">6abdd4e471be48fe</t>
         </is>
       </c>
       <c r="B82" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">bd5e3d25943044e2</t>
+          <t xml:space="preserve">dbda8e2c16fd44c0</t>
         </is>
       </c>
       <c r="C82" s="0" t="inlineStr">
@@ -7241,12 +7241,12 @@
     <row r="83">
       <c r="A83" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">3e6620f882974781</t>
+          <t xml:space="preserve">cc985d7430ee4516</t>
         </is>
       </c>
       <c r="B83" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">bd5e3d25943044e2</t>
+          <t xml:space="preserve">dbda8e2c16fd44c0</t>
         </is>
       </c>
       <c r="C83" s="0" t="inlineStr">
@@ -7314,12 +7314,12 @@
     <row r="84">
       <c r="A84" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">c1feb53fb2804a23</t>
+          <t xml:space="preserve">299eec76cd3e4729</t>
         </is>
       </c>
       <c r="B84" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">bd5e3d25943044e2</t>
+          <t xml:space="preserve">dbda8e2c16fd44c0</t>
         </is>
       </c>
       <c r="C84" s="0" t="inlineStr">
@@ -7387,12 +7387,12 @@
     <row r="85">
       <c r="A85" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">12cea7c1ce354db8</t>
+          <t xml:space="preserve">94de37276a674e6b</t>
         </is>
       </c>
       <c r="B85" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">bd5e3d25943044e2</t>
+          <t xml:space="preserve">dbda8e2c16fd44c0</t>
         </is>
       </c>
       <c r="C85" s="0" t="inlineStr">
@@ -7460,12 +7460,12 @@
     <row r="86">
       <c r="A86" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">ecf0e0aa9e1e43d5</t>
+          <t xml:space="preserve">dd032d1200a44e27</t>
         </is>
       </c>
       <c r="B86" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">bd5e3d25943044e2</t>
+          <t xml:space="preserve">dbda8e2c16fd44c0</t>
         </is>
       </c>
       <c r="C86" s="0" t="inlineStr">
@@ -7533,12 +7533,12 @@
     <row r="87">
       <c r="A87" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">4ebf2ff8e0854802</t>
+          <t xml:space="preserve">7d65236ee0494843</t>
         </is>
       </c>
       <c r="B87" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">bd5e3d25943044e2</t>
+          <t xml:space="preserve">dbda8e2c16fd44c0</t>
         </is>
       </c>
       <c r="C87" s="0" t="inlineStr">
@@ -7606,12 +7606,12 @@
     <row r="88">
       <c r="A88" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">e2cc8d607bcd4813</t>
+          <t xml:space="preserve">39fac7bc0e644bb4</t>
         </is>
       </c>
       <c r="B88" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">bd5e3d25943044e2</t>
+          <t xml:space="preserve">dbda8e2c16fd44c0</t>
         </is>
       </c>
       <c r="C88" s="0" t="inlineStr">
@@ -7679,12 +7679,12 @@
     <row r="89">
       <c r="A89" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">ad819f4d34034780</t>
+          <t xml:space="preserve">678a845213b748bd</t>
         </is>
       </c>
       <c r="B89" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">bd5e3d25943044e2</t>
+          <t xml:space="preserve">dbda8e2c16fd44c0</t>
         </is>
       </c>
       <c r="C89" s="0" t="inlineStr">
@@ -7752,12 +7752,12 @@
     <row r="90">
       <c r="A90" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">a11d4065dfe04c73</t>
+          <t xml:space="preserve">aed90bc4d82744af</t>
         </is>
       </c>
       <c r="B90" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">bd5e3d25943044e2</t>
+          <t xml:space="preserve">dbda8e2c16fd44c0</t>
         </is>
       </c>
       <c r="C90" s="0" t="inlineStr">
